--- a/ExcelTool/LubanTools/DataTables/Datas/NpcSpawnRuleData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcSpawnRuleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3770B3F9-85CC-4BA6-AA12-16964F397A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6F8685-205F-4E16-98B3-6F413E458878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1030" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,10 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">FavorRange   </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -132,10 +128,6 @@
   </si>
   <si>
     <t>0,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -567,10 +559,10 @@
         <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -581,7 +573,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -590,13 +582,13 @@
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5">
@@ -616,13 +608,13 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5">
@@ -630,19 +622,19 @@
         <v>20000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2">
         <v>10001</v>
       </c>
       <c r="E4" s="4">
-        <v>10003</v>
+        <v>10029</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -653,19 +645,19 @@
         <v>20001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <v>10002</v>
       </c>
       <c r="E5" s="4">
-        <v>10003</v>
+        <v>10029</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcSpawnRuleData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcSpawnRuleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6F8685-205F-4E16-98B3-6F413E458878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C21BDF-DD7B-4B12-B6DF-08A283030242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7900" yWindow="3740" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,14 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">FavorRange   </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeelingRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Priority</t>
   </si>
   <si>
@@ -92,33 +84,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>好感度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>心情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>中午客厅马吉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,15 +92,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>vector2#sep=,</t>
+    <t xml:space="preserve">UnlockConditionsID  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁条件表ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,7 +108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,27 +128,6 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -233,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -241,10 +185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="2"/>
@@ -535,11 +476,10 @@
     <col min="4" max="4" width="13.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.1640625" customWidth="1"/>
-    <col min="8" max="8" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -556,16 +496,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -573,7 +510,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -582,16 +519,13 @@
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.5">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -608,58 +542,49 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.5">
+    <row r="4" spans="1:7" ht="16.5">
       <c r="B4" s="2">
         <v>20000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2">
         <v>10001</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>10029</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5">
+    <row r="5" spans="1:7" ht="16.5">
       <c r="B5" s="2">
         <v>20001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>10002</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>10029</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
         <v>1</v>
       </c>
     </row>
